--- a/Unity/Assets/Config/Excel/EquipStrenghtConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipStrenghtConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22110" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="EquipStrenghtProto" sheetId="1" r:id="rId1"/>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8">
-        <v>5</v>
+        <v>50000</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>18</v>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8">
-        <v>10</v>
+        <v>100000</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>20</v>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8">
-        <v>20</v>
+        <v>200000</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>21</v>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8">
-        <v>40</v>
+        <v>400000</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>22</v>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8">
-        <v>80</v>
+        <v>800000</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>23</v>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8">
-        <v>160</v>
+        <v>1600000</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>24</v>
@@ -7256,7 +7256,7 @@
         <v>25</v>
       </c>
       <c r="I12" s="8">
-        <v>320</v>
+        <v>3200000</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>26</v>

--- a/Unity/Assets/Config/Excel/EquipStrenghtConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipStrenghtConfig.xlsx
@@ -135,10 +135,10 @@
     <t>JumpPoint</t>
   </si>
   <si>
-    <t>CostJubin</t>
+    <t>CostJinbi</t>
   </si>
   <si>
-    <t>CostItem</t>
+    <t>CostItems</t>
   </si>
   <si>
     <t>int</t>
